--- a/outputs/Residencial_Dom_Felipe_000000_seens.xlsx
+++ b/outputs/Residencial_Dom_Felipe_000000_seens.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:L87"/>
+  <dimension ref="A5:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="3" max="3"/>
@@ -579,629 +579,549 @@
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>37.379,10 100,00</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="n">
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
         <v>37379.1</v>
       </c>
     </row>
     <row r="23">
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>74758.2</v>
+          <t>(-) CONSERVA��O E MANUTEN��O</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>(-) CONSERVA��O E MANUTEN��O</t>
-        </is>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>MATERIAL DE LIMPEZA - CONDOR - ESPONJA/DESODORANTE/LIMPADOR 01/2026 05/02/2026 DBITO 867805 42,36</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>42.36</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>MATERIAL DE LIMPEZA - CONDOR - ESPONJA/DESODORANTE/LIMPADOR 01/2026 05/02/2026 DBITO 867805 42,36</t>
+          <t>- SACO E 01/2026 02/02/2026 BOLETO 6881 351,18</t>
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>42.36</v>
+        <v>351.18</v>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>- SACO E 01/2026 02/02/2026 BOLETO 6881 351,18</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>351.18</v>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>393.54</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>393.54</v>
+          <t>(-) LIXO/DESINFETANTE/ �GUA SANIT�RIA /HIPOCLORITO</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>(-) LIXO/DESINFETANTE/ �GUA SANIT�RIA /HIPOCLORITO</t>
-        </is>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>- FLOR NATURA 01/2026 03/02/2026 DBITO 74269 59,97</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>59.97</v>
       </c>
     </row>
     <row r="29">
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>- FLOR NATURA 01/2026 03/02/2026 DBITO 74269 59,97</t>
+          <t>JARDIM - ACAPUCO DISTRIBUIDORA DE VASOS E ARTIGOS - SACOS DE 01/2026 25/02/2026 DBITO 45,00</t>
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>59.97</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30">
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>JARDIM - ACAPUCO DISTRIBUIDORA DE VASOS E ARTIGOS - SACOS DE 01/2026 25/02/2026 DBITO 45,00</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>45</v>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>104.97</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>104.97</v>
+          <t>(-) TERRA</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>(-) TERRA</t>
-        </is>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>JARDIM - FLORES ESTAO - FLORES 01/2026 25/02/2026 DBITO 125,00</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="33">
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>JARDIM - FLORES ESTAO - FLORES 01/2026 25/02/2026 DBITO 125,00</t>
+          <t>- FLORES DIVERSAS 01/2026 25/02/2026 DBITO 60,00</t>
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>125</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>- FLORES DIVERSAS 01/2026 25/02/2026 DBITO 60,00</t>
+          <t>MATERIAL ELTRICO - SENDAS DISTRIBUIDORA - BALDE 01/2026 10/02/2026 DBITO 263411 13,90</t>
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>60</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="35">
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>MATERIAL ELTRICO - SENDAS DISTRIBUIDORA - BALDE 01/2026 10/02/2026 DBITO 263411 13,90</t>
+          <t>SEGURO PREDIAL - TOKIO MARINE SEGURADORA - P.06/06 01/2026 25/02/2026 BOLETO 820,02</t>
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>13.9</v>
+        <v>820.02</v>
       </c>
     </row>
     <row r="36">
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>SEGURO PREDIAL - TOKIO MARINE SEGURADORA - P.06/06 01/2026 25/02/2026 BOLETO 820,02</t>
+          <t>- GASOLINA COMUM 01/2026 10/02/2026 DBITO 587136 31,97</t>
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>820.02</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>- GASOLINA COMUM 01/2026 10/02/2026 DBITO 587136 31,97</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>31.97</v>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>1050.89</v>
       </c>
     </row>
     <row r="38">
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>1.549,40</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>1549.4</v>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS ADMINISTRATIVAS</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>2600.29</v>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>HONORRIOS SNDICO (A) - VACILINA VOLOCHEN 01/2026 02/02/2026 PIX 1.000,00</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>(-) DESPESAS ADMINISTRATIVAS</t>
-        </is>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>HONORRIOS ADMINISTRATIVOS - EG CONDOMNIO 01/2026 02/02/2026TRANSFERNCIA 1.188,84</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>1188.84</v>
       </c>
     </row>
     <row r="41">
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>HONORRIOS SNDICO (A) - VACILINA VOLOCHEN 01/2026 02/02/2026 PIX 1.000,00</t>
+          <t>MAT. EXPEDIENTE - PAPELARIA BOM JESUS - XEROX/ PLATIFICAO 01/2026 02/02/2026 DBITO 10,00</t>
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>HONORRIOS ADMINISTRATIVOS - EG CONDOMNIO 01/2026 02/02/2026TRANSFERNCIA 1.188,84</t>
+          <t>CPIAS/IMPRESSES - INFOCOPY - XEROX 01/2026 02/02/2026TRANSFERNCIA 4,50</t>
         </is>
       </c>
       <c r="L42" s="3" t="n">
-        <v>1188.84</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="43">
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>MAT. EXPEDIENTE - PAPELARIA BOM JESUS - XEROX/ PLATIFICAO 01/2026 02/02/2026 DBITO 10,00</t>
+          <t>CPIAS/IMPRESSES - DRI COLOR - XEROX 01/2026 10/02/2026 DBITO 4,00</t>
         </is>
       </c>
       <c r="L43" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>CPIAS/IMPRESSES - INFOCOPY - XEROX 01/2026 02/02/2026TRANSFERNCIA 4,50</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>4.5</v>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>2207.34</v>
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>CPIAS/IMPRESSES - DRI COLOR - XEROX 01/2026 10/02/2026 DBITO 4,00</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>4</v>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS POR CONSUMO</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2.207,34</t>
+          <t>GS - NACIONAL GS BUTANO - QTD. 142 UNIT. 7,35 01/2026 25/02/2026 BOLETO 20272 1.043,70</t>
         </is>
       </c>
       <c r="L46" s="3" t="n">
-        <v>2207.34</v>
+        <v>1043.7</v>
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>4414.68</v>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>ENERGIA - COPEL - CONDOMNIO (83557202) CONS. 408 KWH 01/2026 09/02/2026 DBITO AUT. 400,27</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>400.27</v>
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>(-) DESPESAS POR CONSUMO</t>
-        </is>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>GUA - SANEPAR - BLOCO A (27980473) CONS 159 M 01/2026 09/02/2026 DBITO AUT. 1.833,31</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>1833.31</v>
       </c>
     </row>
     <row r="49">
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>GS - NACIONAL GS BUTANO - QTD. 142 UNIT. 7,35 01/2026 25/02/2026 BOLETO 20272 1.043,70</t>
+          <t>GUA - SANEPAR - BLOCO B (27980449) CONS 149 M 01/2026 09/02/2026 DBITO AUT. 1.802,60</t>
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>1043.7</v>
+        <v>1802.6</v>
       </c>
     </row>
     <row r="50">
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>ENERGIA - COPEL - CONDOMNIO (83557202) CONS. 408 KWH 01/2026 09/02/2026 DBITO AUT. 400,27</t>
+          <t>GUA - SANEPAR - BLOCO C (27732488) CONS 126 M 01/2026 06/02/2026 DBITO AUT. 1.731,97</t>
         </is>
       </c>
       <c r="L50" s="3" t="n">
-        <v>400.27</v>
+        <v>1731.97</v>
       </c>
     </row>
     <row r="51">
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>GUA - SANEPAR - BLOCO A (27980473) CONS 159 M 01/2026 09/02/2026 DBITO AUT. 1.833,31</t>
+          <t>GUA - SANEPAR - BLOCO D (27732500) CONS 148 M 01/2026 06/02/2026 DBITO AUT. 1.743,89</t>
         </is>
       </c>
       <c r="L51" s="3" t="n">
-        <v>1833.31</v>
+        <v>1743.89</v>
       </c>
     </row>
     <row r="52">
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>GUA - SANEPAR - BLOCO B (27980449) CONS 149 M 01/2026 09/02/2026 DBITO AUT. 1.802,60</t>
+          <t>GUA - SANEPAR - SALO (02616530) CONS 5 M 01/2026 09/02/2026 DBITO AUT. 99,42</t>
         </is>
       </c>
       <c r="L52" s="3" t="n">
-        <v>1802.6</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="53">
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>GUA - SANEPAR - BLOCO C (27732488) CONS 126 M 01/2026 06/02/2026 DBITO AUT. 1.731,97</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>1731.97</v>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>8655.16</v>
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>GUA - SANEPAR - BLOCO D (27732500) CONS 148 M 01/2026 06/02/2026 DBITO AUT. 1.743,89</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>1743.89</v>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS N�O RATEADAS</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>GUA - SANEPAR - SALO (02616530) CONS 5 M 01/2026 09/02/2026 DBITO AUT. 99,42</t>
+          <t>- AQUISIO DE UMA 11/2025 10/02/2026 BOLETO 10009 281,93</t>
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>99.42</v>
+        <v>281.93</v>
       </c>
     </row>
     <row r="56">
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>8.655,16</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="n">
-        <v>8655.16</v>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>281.93</v>
       </c>
     </row>
     <row r="57">
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L57" s="4" t="n">
-        <v>17310.32</v>
+          <t>(-) RO�ADEIRA</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>(-) DESPESAS N�O RATEADAS</t>
-        </is>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>- CAIXA DE GORDURA INSS 01/2026 19/02/2026 GUIA 25 77,00</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="59">
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>- AQUISIO DE UMA 11/2025 10/02/2026 BOLETO 10009 281,93</t>
+          <t>- CONTROLE DE PRGAS 01/2026 04/02/2026 BOLETO 25 623,00</t>
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>281.93</v>
+        <v>623</v>
       </c>
     </row>
     <row r="60">
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v>281.93</v>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>PORTO - NEY BRAGA - CONSERTO LEITOR TAG PORTO DE ENTRADA 01/2026 25/02/2026 PIX 492 310,00</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>310</v>
       </c>
     </row>
     <row r="61">
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>(-) RO�ADEIRA</t>
-        </is>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>PLAYGROUND - J CORDOVA AGRONEGOCIOS - INFANTIL DE MADEIRA 01/2026 20/02/2026 PIX 2.300,00</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>2300</v>
       </c>
     </row>
     <row r="62">
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>- CAIXA DE GORDURA INSS 01/2026 19/02/2026 GUIA 25 77,00</t>
+          <t>MATERIAIS - RODRIGO LAZZARATI - P. 01/02 01/2026 19/02/2026 BOLETO 37 956,46</t>
         </is>
       </c>
       <c r="L62" s="3" t="n">
-        <v>77</v>
+        <v>956.46</v>
       </c>
     </row>
     <row r="63">
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>- CONTROLE DE PRGAS 01/2026 04/02/2026 BOLETO 25.623,00</t>
-        </is>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>25623</v>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>4266.46</v>
       </c>
     </row>
     <row r="64">
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>PORTO - NEY BRAGA - CONSERTO LEITOR TAG PORTO DE ENTRADA 01/2026 25/02/2026 PIX 492.310,00</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>492310</v>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>(-) M�VEIS E UTENS�LIOS</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>PLAYGROUND - J CORDOVA AGRONEGOCIOS - INFANTIL DE MADEIRA 01/2026 20/02/2026 PIX 2.300,00</t>
+          <t>- VASO GREGO 01/2026 03/02/2026 DBITO 79768 44,97</t>
         </is>
       </c>
       <c r="L65" s="3" t="n">
-        <v>2300</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="66">
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>MATERIAIS - RODRIGO LAZZARATI - P. 01/02 01/2026 19/02/2026 BOLETO 37.956,46</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>37956.46</v>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>44.97</v>
       </c>
     </row>
     <row r="67">
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>4.548,39</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="n">
-        <v>4548.39</v>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>(-) CONTRATOS FIXOS</t>
+        </is>
       </c>
     </row>
     <row r="68">
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="n">
-        <v>562814.85</v>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>- SERVIOS PRESTADOS 01/2026 11/02/2026 BOLETO 118 15.284,86</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>15284.86</v>
       </c>
     </row>
     <row r="69">
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>(-) M�VEIS E UTENS�LIOS</t>
-        </is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>15284.86</v>
       </c>
     </row>
     <row r="70">
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>- VASO GREGO 01/2026 03/02/2026 DBITO 79768 44,97</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="n">
-        <v>44.97</v>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS BANC�RIAS</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>44,97</t>
+          <t>DESPESAS BANCRIAS - CEF - DB CEST 02/2026 05/02/2026 DBITO AUT. 75,00</t>
         </is>
       </c>
       <c r="L71" s="3" t="n">
-        <v>44.97</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72">
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L72" s="4" t="n">
-        <v>89.94</v>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>DESPESAS BANCRIAS - CEF - TAR PIX 02/2026 02/02/2026 DBITO AUT. 8,50</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="73">
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>(-) CONTRATOS FIXOS</t>
-        </is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>83.5</v>
       </c>
     </row>
     <row r="74">
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>- SERVIOS PRESTADOS 01/2026 11/02/2026 BOLETO 118 15.284,86</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>15284.86</v>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL RECEITAS DO MÊS</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>37379.1</v>
       </c>
     </row>
     <row r="75">
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>15.284,86</t>
-        </is>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>15284.86</v>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL DESPESAS DO MÊS</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>32373.62</v>
       </c>
     </row>
     <row r="76">
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L76" s="4" t="n">
-        <v>30569.72</v>
+          <t>RESUMO DO MÊS</t>
+        </is>
       </c>
     </row>
     <row r="77">
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>(-) DESPESAS BANC�RIAS</t>
-        </is>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>37379.1</v>
       </c>
     </row>
     <row r="78">
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>DESPESAS BANCRIAS - CEF - DB CEST 02/2026 05/02/2026 DBITO AUT. 75,00</t>
+          <t>DESPESAS</t>
         </is>
       </c>
       <c r="L78" s="3" t="n">
-        <v>75</v>
+        <v>32373.62</v>
       </c>
     </row>
     <row r="79">
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>DESPESAS BANCRIAS - CEF - TAR PIX 02/2026 02/02/2026 DBITO AUT. 8,50</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>83,50</t>
-        </is>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>83.5</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L81" s="4" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL RECEITAS DO MÊS</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="n">
-        <v>37379.1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL DESPESAS DO MÊS</t>
-        </is>
-      </c>
-      <c r="L83" s="4" t="n">
-        <v>32373.62</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>RESUMO DO MÊS</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>RECEITAS</t>
-        </is>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>37379.1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>DESPESAS</t>
-        </is>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>32373.62</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>TOTAL (RECEITAS - DESPESAS)</t>
         </is>
       </c>
-      <c r="L87" s="4" t="n">
+      <c r="L79" s="4" t="n">
         <v>5005.48</v>
       </c>
     </row>

--- a/outputs/Residencial_Dom_Felipe_000000_seens.xlsx
+++ b/outputs/Residencial_Dom_Felipe_000000_seens.xlsx
@@ -474,7 +474,7 @@
     <row r="11">
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>(+) RECEITAS</t>
+          <t>(+) (+) RECEITAS</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
     <row r="14">
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>GS 2.560,67 6,85</t>
+          <t>GÁS 2.560,67 6,85</t>
         </is>
       </c>
       <c r="L14" s="3" t="n">
@@ -521,7 +521,7 @@
     <row r="16">
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>GUA 7.111,83 19,03</t>
+          <t>ÁGUA 7.111,83 19,03</t>
         </is>
       </c>
       <c r="L16" s="3" t="n">
@@ -591,7 +591,7 @@
     <row r="23">
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>(-) CONSERVA��O E MANUTEN��O</t>
+          <t>(-) CONSERVAÇÃO E MANUTENÇÃO</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
     <row r="27">
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>(-) LIXO/DESINFETANTE/ �GUA SANIT�RIA /HIPOCLORITO</t>
+          <t>(-) MATERIAL DE LIMPEZA</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="31">
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>(-) TERRA</t>
+          <t>(-) (-) (-) (-) JARDINAGEM</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
     <row r="38">
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>(-) DESPESAS ADMINISTRATIVAS</t>
+          <t>(-) (-) DESPESAS ADMINISTRATIVAS</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
     <row r="48">
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>GUA - SANEPAR - BLOCO A (27980473) CONS 159 M 01/2026 09/02/2026 DBITO AUT. 1.833,31</t>
+          <t>ÁGUA - SANEPAR - BLOCO A (27980473) CONS 159 M 01/2026 09/02/2026 DBITO AUT. 1.833,31</t>
         </is>
       </c>
       <c r="L48" s="3" t="n">
@@ -836,7 +836,7 @@
     <row r="49">
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>GUA - SANEPAR - BLOCO B (27980449) CONS 149 M 01/2026 09/02/2026 DBITO AUT. 1.802,60</t>
+          <t>ÁGUA - SANEPAR - BLOCO B (27980449) CONS 149 M 01/2026 09/02/2026 DBITO AUT. 1.802,60</t>
         </is>
       </c>
       <c r="L49" s="3" t="n">
@@ -846,7 +846,7 @@
     <row r="50">
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>GUA - SANEPAR - BLOCO C (27732488) CONS 126 M 01/2026 06/02/2026 DBITO AUT. 1.731,97</t>
+          <t>ÁGUA - SANEPAR - BLOCO C (27732488) CONS 126 M 01/2026 06/02/2026 DBITO AUT. 1.731,97</t>
         </is>
       </c>
       <c r="L50" s="3" t="n">
@@ -856,7 +856,7 @@
     <row r="51">
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>GUA - SANEPAR - BLOCO D (27732500) CONS 148 M 01/2026 06/02/2026 DBITO AUT. 1.743,89</t>
+          <t>ÁGUA - SANEPAR - BLOCO D (27732500) CONS 148 M 01/2026 06/02/2026 DBITO AUT. 1.743,89</t>
         </is>
       </c>
       <c r="L51" s="3" t="n">
@@ -866,7 +866,7 @@
     <row r="52">
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>GUA - SANEPAR - SALO (02616530) CONS 5 M 01/2026 09/02/2026 DBITO AUT. 99,42</t>
+          <t>ÁGUA - SANEPAR - SALO (02616530) CONS 5 M 01/2026 09/02/2026 DBITO AUT. 99,42</t>
         </is>
       </c>
       <c r="L52" s="3" t="n">
@@ -886,14 +886,14 @@
     <row r="54">
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>(-) DESPESAS N�O RATEADAS</t>
+          <t>(-) (-) DESPESAS NÃO RATEADAS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>- AQUISIO DE UMA 11/2025 10/02/2026 BOLETO 10009 281,93</t>
+          <t>- AQUISIO DE UMA ROÇADEIRA 11/2025 10/02/2026 BOLETO 10009 281,93</t>
         </is>
       </c>
       <c r="L55" s="3" t="n">
@@ -913,7 +913,7 @@
     <row r="57">
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>(-) RO�ADEIRA</t>
+          <t>(-) OUTROS MATERIAIS</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
     <row r="64">
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>(-) M�VEIS E UTENS�LIOS</t>
+          <t>(-) MÓVEIS E UTENSÍLIOS</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <row r="70">
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>(-) DESPESAS BANC�RIAS</t>
+          <t>(-) DESPESAS BANCÁRIAS</t>
         </is>
       </c>
     </row>

--- a/outputs/Residencial_Dom_Felipe_000000_seens.xlsx
+++ b/outputs/Residencial_Dom_Felipe_000000_seens.xlsx
@@ -474,7 +474,7 @@
     <row r="11">
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>(+) (+) RECEITAS</t>
+          <t>(+) RECEITAS</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
     <row r="14">
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>GÁS 2.560,67 6,85</t>
+          <t>GS 2.560,67 6,85</t>
         </is>
       </c>
       <c r="L14" s="3" t="n">
@@ -521,7 +521,7 @@
     <row r="16">
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ÁGUA 7.111,83 19,03</t>
+          <t>GUA 7.111,83 19,03</t>
         </is>
       </c>
       <c r="L16" s="3" t="n">
@@ -591,7 +591,7 @@
     <row r="23">
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>(-) CONSERVAÇÃO E MANUTENÇÃO</t>
+          <t>(-) CONSERVA��O E MANUTEN��O</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
     <row r="27">
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>(-) MATERIAL DE LIMPEZA</t>
+          <t>(-) LIXO/DESINFETANTE/ �GUA SANIT�RIA /HIPOCLORITO</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="31">
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>(-) (-) (-) (-) JARDINAGEM</t>
+          <t>(-) TERRA</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
     <row r="38">
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>(-) (-) DESPESAS ADMINISTRATIVAS</t>
+          <t>(-) DESPESAS ADMINISTRATIVAS</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
     <row r="48">
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>ÁGUA - SANEPAR - BLOCO A (27980473) CONS 159 M 01/2026 09/02/2026 DBITO AUT. 1.833,31</t>
+          <t>GUA - SANEPAR - BLOCO A (27980473) CONS 159 M 01/2026 09/02/2026 DBITO AUT. 1.833,31</t>
         </is>
       </c>
       <c r="L48" s="3" t="n">
@@ -836,7 +836,7 @@
     <row r="49">
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>ÁGUA - SANEPAR - BLOCO B (27980449) CONS 149 M 01/2026 09/02/2026 DBITO AUT. 1.802,60</t>
+          <t>GUA - SANEPAR - BLOCO B (27980449) CONS 149 M 01/2026 09/02/2026 DBITO AUT. 1.802,60</t>
         </is>
       </c>
       <c r="L49" s="3" t="n">
@@ -846,7 +846,7 @@
     <row r="50">
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>ÁGUA - SANEPAR - BLOCO C (27732488) CONS 126 M 01/2026 06/02/2026 DBITO AUT. 1.731,97</t>
+          <t>GUA - SANEPAR - BLOCO C (27732488) CONS 126 M 01/2026 06/02/2026 DBITO AUT. 1.731,97</t>
         </is>
       </c>
       <c r="L50" s="3" t="n">
@@ -856,7 +856,7 @@
     <row r="51">
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>ÁGUA - SANEPAR - BLOCO D (27732500) CONS 148 M 01/2026 06/02/2026 DBITO AUT. 1.743,89</t>
+          <t>GUA - SANEPAR - BLOCO D (27732500) CONS 148 M 01/2026 06/02/2026 DBITO AUT. 1.743,89</t>
         </is>
       </c>
       <c r="L51" s="3" t="n">
@@ -866,7 +866,7 @@
     <row r="52">
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>ÁGUA - SANEPAR - SALO (02616530) CONS 5 M 01/2026 09/02/2026 DBITO AUT. 99,42</t>
+          <t>GUA - SANEPAR - SALO (02616530) CONS 5 M 01/2026 09/02/2026 DBITO AUT. 99,42</t>
         </is>
       </c>
       <c r="L52" s="3" t="n">
@@ -886,14 +886,14 @@
     <row r="54">
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>(-) (-) DESPESAS NÃO RATEADAS</t>
+          <t>(-) DESPESAS N�O RATEADAS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>- AQUISIO DE UMA ROÇADEIRA 11/2025 10/02/2026 BOLETO 10009 281,93</t>
+          <t>- AQUISIO DE UMA 11/2025 10/02/2026 BOLETO 10009 281,93</t>
         </is>
       </c>
       <c r="L55" s="3" t="n">
@@ -913,7 +913,7 @@
     <row r="57">
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>(-) OUTROS MATERIAIS</t>
+          <t>(-) RO�ADEIRA</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
     <row r="64">
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>(-) MÓVEIS E UTENSÍLIOS</t>
+          <t>(-) M�VEIS E UTENS�LIOS</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
     <row r="70">
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>(-) DESPESAS BANCÁRIAS</t>
+          <t>(-) DESPESAS BANC�RIAS</t>
         </is>
       </c>
     </row>
